--- a/stories/arbres/TREE-SOC-005.xlsx
+++ b/stories/arbres/TREE-SOC-005.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hugo est à l'école, avec maman. Dans le sac, un petit livre. Maman dit : si on veut acheter quelque chose, on demande. On demande à l'adulte. Papa ou maman. Hugo répète : demander. Adulte. L'argent se range. Maman range le porte-monnaie. On demande à papa ou maman, l'adulte, avant un achat.</t>
+          <t>Hugo est à l'école, avec maman. Dans le sac, un petit livre. Si on veut acheter quelque chose, on demande. On demande à l'adulte. Papa ou maman. Hugo répète : demander. Adulte. L'argent se range. Maman range le porte-monnaie. On demande à papa ou maman, l'adulte, avant un achat.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo est à l'école, avec maman. Dans le sac, un petit livre.
+maman|Si on veut acheter quelque chose, on demande. On demande à l'adulte. Papa ou maman.
+narrateur|Hugo répète : demander. Adulte. L'argent se range. Maman range le porte-monnaie. On demande à papa ou maman, l'adulte, avant un achat.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1511,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1540,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. Hugo voit un crayon joli. Maman dit : on demande à l'adulte. Hugo dit : je demande. Maman écoute. On demande à papa ou maman, l'adulte, avant un achat.</t>
+          <t>C'est le matin. Hugo voit un crayon joli. On demande à l'adulte. Je demande. Maman écoute. On demande à papa ou maman, l'adulte, avant un achat.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1678,13 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Hugo voit un crayon joli.
+maman|On demande à l'adulte.
+enfant-m|Je demande. Maman écoute. On demande à papa ou maman, l'adulte, avant un achat.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1861,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|On veut un crayon. On fait quoi ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2034,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a demandé. L'adulte a écouté. Demander. On demande à papa ou maman, l'adulte, avant un achat.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2225,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2392,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo va vers la cuisine. Des miettes dorment sur la table. Dans la cuisine, Hugo voit un gâteau. Hugo demande à l'adulte. Maman écoute. On demande à papa ou maman, l'adulte, avant un achat.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2527,6 +2583,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2689,6 +2750,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo garde le ballon rouge tout près. La lumière est claire. On souffle doucement. On a demandé à l'adulte. Papa ou maman. L'argent est rangé. On demande à papa ou maman, l'adulte, avant un achat. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2851,6 +2917,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3013,6 +3084,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo garde le seau bleu tout près. Des miettes dorment sur la table. On écoute jusqu'au bout. On a demandé à l'adulte. Papa ou maman. La main de l'adulte était là. On demande à papa ou maman, l'adulte, avant un achat. Maman serre Hugo tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3175,6 +3251,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3199,7 +3280,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Hugo garde le doudou tout près. Un chat miaule une fois. On attend son tour. On a demandé à l'adulte. Papa ou maman. On a dit : je demande. On demande à papa ou maman, l'adulte, avant un achat. Papa n'est pas loin. On rentre.</t>
+          <t>Hugo garde le doudou tout près. Un chat miaule une fois. On attend son tour. On a demandé à l'adulte. Papa ou maman. On Je demande. On demande à papa ou maman, l'adulte, avant un achat. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3337,6 +3418,12 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo garde le doudou tout près. Un chat miaule une fois. On attend son tour. On a demandé à l'adulte. Papa ou maman. On
+enfant-f|Je demande. On demande à papa ou maman, l'adulte, avant un achat. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3499,6 +3586,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3661,6 +3753,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo va vers le jardin. Un nuage passe lentement. Dans le jardin, une fleur. Hugo demande avant de cueillir. Adulte. On demande à papa ou maman, l'adulte, avant un achat.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3847,6 +3944,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3871,7 +3973,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Hugo garde le ballon rouge tout près. Les chaussures font toc toc. On sourit ensemble. On a demandé à l'adulte. Papa ou maman. L'adulte a écouté. On demande à papa ou maman, l'adulte, avant un achat. Hugo range. Maman dit : c'est bien.</t>
+          <t>Hugo garde le ballon rouge tout près. Les chaussures font toc toc. On sourit ensemble. On a demandé à l'adulte. Papa ou maman. L'adulte a écouté. On demande à papa ou maman, l'adulte, avant un achat. Hugo range. C'est bien.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4009,6 +4111,12 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo garde le ballon rouge tout près. Les chaussures font toc toc. On sourit ensemble. On a demandé à l'adulte. Papa ou maman. L'adulte a écouté. On demande à papa ou maman, l'adulte, avant un achat. Hugo range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4171,6 +4279,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4333,6 +4446,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo garde le seau bleu tout près. La couverture est douce. On pose les pieds par terre. On a demandé à l'adulte. Papa ou maman. L'argent est rangé. On demande à papa ou maman, l'adulte, avant un achat. On souffle. Hugo sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4495,6 +4613,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4657,6 +4780,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo garde le doudou tout près. Une cloche tinte au loin. On parle tout bas. On a demandé à l'adulte. Papa ou maman. La main de l'adulte était là. On demande à papa ou maman, l'adulte, avant un achat. Hugo prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4819,6 +4947,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4843,7 +4976,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Hugo va vers la chambre. L'eau fait un petit bruit. Dans la chambre, un livre neuf. Hugo demande. L'adulte dit : on verra. On demande à papa ou maman, l'adulte, avant un achat.</t>
+          <t>Hugo va vers la chambre. L'eau fait un petit bruit. Dans la chambre, un livre neuf. Hugo demande. On verra. On demande à papa ou maman, l'adulte, avant un achat.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -4981,6 +5114,12 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo va vers la chambre. L'eau fait un petit bruit. Dans la chambre, un livre neuf. Hugo demande.
+enfant-f|On verra. On demande à papa ou maman, l'adulte, avant un achat.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5167,6 +5306,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5191,7 +5335,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Hugo garde le ballon rouge tout près. Le bois sent le chaud. On range les jouets. On a demandé à l'adulte. Papa ou maman. On a dit : je demande. On demande à papa ou maman, l'adulte, avant un achat. Hugo dit merci à maman. On rentre.</t>
+          <t>Hugo garde le ballon rouge tout près. Le bois sent le chaud. On range les jouets. On a demandé à l'adulte. Papa ou maman. On Je demande. On demande à papa ou maman, l'adulte, avant un achat. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5329,6 +5473,13 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo garde le ballon rouge tout près. Le bois sent le chaud. On range les jouets. On a demandé à l'adulte. Papa ou maman. On
+enfant-f|Je demande. On demande à papa ou maman, l'adulte, avant un achat.
+narrateur|Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5491,6 +5642,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5653,6 +5809,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo garde le seau bleu tout près. Une goutte tombe, ploc. On s'assoit un moment. On a demandé à l'adulte. Papa ou maman. L'adulte a écouté. On demande à papa ou maman, l'adulte, avant un achat. Maman serre Hugo tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5815,6 +5976,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5977,6 +6143,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo garde le doudou tout près. Le savon sent la fleur. On respire, un, deux. On a demandé à l'adulte. Papa ou maman. L'argent est rangé. On demande à papa ou maman, l'adulte, avant un achat. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6139,6 +6310,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6301,6 +6477,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Après la sieste, un autocollant brille. Hugo va vers maman. Hugo demande. L'adulte écoute. On décide ensemble. On demande à papa ou maman, l'adulte, avant un achat.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6479,6 +6660,11 @@
           <t>question d'écoute, ne change pas le cours</t>
         </is>
       </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|À qui on demande ?</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6503,7 +6689,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>À maman. L'adulte. Hugo a dit : je demande. On demande à papa ou maman, l'adulte, avant un achat.</t>
+          <t>À maman. L'adulte. Hugo Je demande. On demande à papa ou maman, l'adulte, avant un achat.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6645,6 +6831,12 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|À maman. L'adulte. Hugo
+enfant-f|Je demande. On demande à papa ou maman, l'adulte, avant un achat.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6831,6 +7023,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6993,6 +7190,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo va vers la cuisine. L'herbe chatouille le mollet. Ça sent le pain. Hugo demande. Adulte. Maman sourit. On demande à papa ou maman, l'adulte, avant un achat.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7179,6 +7381,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7203,7 +7410,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Hugo garde le ballon rouge tout près. Le tissu est tout doux. On referme le sac. On a demandé à l'adulte. Papa ou maman. La main de l'adulte était là. On demande à papa ou maman, l'adulte, avant un achat. Hugo range. Maman dit : c'est bien.</t>
+          <t>Hugo garde le ballon rouge tout près. Le tissu est tout doux. On referme le sac. On a demandé à l'adulte. Papa ou maman. La main de l'adulte était là. On demande à papa ou maman, l'adulte, avant un achat. Hugo range. C'est bien.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7341,6 +7548,12 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo garde le ballon rouge tout près. Le tissu est tout doux. On referme le sac. On a demandé à l'adulte. Papa ou maman. La main de l'adulte était là. On demande à papa ou maman, l'adulte, avant un achat. Hugo range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7503,6 +7716,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7527,7 +7745,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Hugo garde le seau bleu tout près. Une cuillère tinte. On essuie une miette. On a demandé à l'adulte. Papa ou maman. On a dit : je demande. On demande à papa ou maman, l'adulte, avant un achat. On souffle. Hugo sourit.</t>
+          <t>Hugo garde le seau bleu tout près. Une cuillère tinte. On essuie une miette. On a demandé à l'adulte. Papa ou maman. On Je demande. On demande à papa ou maman, l'adulte, avant un achat. On souffle. Hugo sourit.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7665,6 +7883,13 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo garde le seau bleu tout près. Une cuillère tinte. On essuie une miette. On a demandé à l'adulte. Papa ou maman. On
+enfant-f|Je demande. On demande à papa ou maman, l'adulte, avant un achat. On souffle.
+narrateur|Hugo sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7827,6 +8052,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7989,6 +8219,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo garde le doudou tout près. Le sable est tiède. On met le doudou près. On a demandé à l'adulte. Papa ou maman. L'adulte a écouté. On demande à papa ou maman, l'adulte, avant un achat. Hugo prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8151,6 +8386,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8313,6 +8553,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo va vers le jardin. La couverture est douce. Une feuille tombe. Hugo demande encore. Demander à l'adulte. On demande à papa ou maman, l'adulte, avant un achat.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8499,6 +8744,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8661,6 +8911,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo garde le ballon rouge tout près. Un rire court, tout petit. On lace les chaussures. On a demandé à l'adulte. Papa ou maman. L'argent est rangé. On demande à papa ou maman, l'adulte, avant un achat. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8823,6 +9078,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8985,6 +9245,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo garde le seau bleu tout près. Le papier froisse, chut. On met le manteau. On a demandé à l'adulte. Papa ou maman. La main de l'adulte était là. On demande à papa ou maman, l'adulte, avant un achat. Maman serre Hugo tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9147,6 +9412,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9171,7 +9441,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Hugo garde le doudou tout près. L'herbe chatouille le mollet. On boit une gorgée. On a demandé à l'adulte. Papa ou maman. On a dit : je demande. On demande à papa ou maman, l'adulte, avant un achat. Papa n'est pas loin. On rentre.</t>
+          <t>Hugo garde le doudou tout près. L'herbe chatouille le mollet. On boit une gorgée. On a demandé à l'adulte. Papa ou maman. On Je demande. On demande à papa ou maman, l'adulte, avant un achat. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9309,6 +9579,12 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo garde le doudou tout près. L'herbe chatouille le mollet. On boit une gorgée. On a demandé à l'adulte. Papa ou maman. On
+enfant-f|Je demande. On demande à papa ou maman, l'adulte, avant un achat. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9471,6 +9747,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9633,6 +9914,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo va vers la chambre. Ça sent le pain tiède. Le doudou écoute. Hugo a demandé. L'adulte était là. On demande à papa ou maman, l'adulte, avant un achat.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9819,6 +10105,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9843,7 +10134,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Hugo garde le ballon rouge tout près. Un pigeon roucoule. On feuillette le livre. On a demandé à l'adulte. Papa ou maman. L'adulte a écouté. On demande à papa ou maman, l'adulte, avant un achat. Hugo range. Maman dit : c'est bien.</t>
+          <t>Hugo garde le ballon rouge tout près. Un pigeon roucoule. On feuillette le livre. On a demandé à l'adulte. Papa ou maman. L'adulte a écouté. On demande à papa ou maman, l'adulte, avant un achat. Hugo range. C'est bien.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -9981,6 +10272,12 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo garde le ballon rouge tout près. Un pigeon roucoule. On feuillette le livre. On a demandé à l'adulte. Papa ou maman. L'adulte a écouté. On demande à papa ou maman, l'adulte, avant un achat. Hugo range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10143,6 +10440,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10305,6 +10607,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo garde le seau bleu tout près. La fenêtre vibre un peu. On referme le livre. On a demandé à l'adulte. Papa ou maman. L'argent est rangé. On demande à papa ou maman, l'adulte, avant un achat. On souffle. Hugo sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10467,6 +10774,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10629,6 +10941,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo garde le doudou tout près. Le lait est froid dans le verre. On pose le ballon. On a demandé à l'adulte. Papa ou maman. La main de l'adulte était là. On demande à papa ou maman, l'adulte, avant un achat. Hugo prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10791,6 +11108,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10953,6 +11275,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, un petit carnet. Hugo prend la main de maman. Hugo demande. Adulte. Maman dit merci d'avoir demandé. On demande à papa ou maman, l'adulte, avant un achat.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11129,6 +11456,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|L'argent, on le prend tout seul ?</t>
         </is>
       </c>
     </row>
@@ -11297,6 +11629,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Demander. Adulte. Hugo a pris la main de maman. On demande à papa ou maman, l'adulte, avant un achat.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11483,6 +11820,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11645,6 +11987,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo va vers la cuisine. Le coussin est moelleux. Hugo pose une tasse. Hugo demande. Adulte. Merci. On demande à papa ou maman, l'adulte, avant un achat.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11831,6 +12178,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11855,7 +12207,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Hugo garde le ballon rouge tout près. La corde du sac est rêche. On secoue le sable. On a demandé à l'adulte. Papa ou maman. On a dit : je demande. On demande à papa ou maman, l'adulte, avant un achat. Hugo dit merci à maman. On rentre.</t>
+          <t>Hugo garde le ballon rouge tout près. La corde du sac est rêche. On secoue le sable. On a demandé à l'adulte. Papa ou maman. On Je demande. On demande à papa ou maman, l'adulte, avant un achat. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -11993,6 +12345,13 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo garde le ballon rouge tout près. La corde du sac est rêche. On secoue le sable. On a demandé à l'adulte. Papa ou maman. On
+enfant-f|Je demande. On demande à papa ou maman, l'adulte, avant un achat.
+narrateur|Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12155,6 +12514,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12317,6 +12681,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo garde le seau bleu tout près. Le savon mousse entre les doigts. On caresse le tissu. On a demandé à l'adulte. Papa ou maman. L'adulte a écouté. On demande à papa ou maman, l'adulte, avant un achat. Maman serre Hugo tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12479,6 +12848,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12641,6 +13015,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo garde le doudou tout près. Un ruisseau chante. On tend la main. On a demandé à l'adulte. Papa ou maman. L'argent est rangé. On demande à papa ou maman, l'adulte, avant un achat. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12803,6 +13182,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12965,6 +13349,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo va vers le jardin. Un vélo passe, toc toc. Le vent est doux. Hugo répète : demander. À l'adulte. On demande à papa ou maman, l'adulte, avant un achat.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13151,6 +13540,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13175,7 +13569,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Hugo garde le ballon rouge tout près. La laine gratte un peu. On chante un petit air. On a demandé à l'adulte. Papa ou maman. La main de l'adulte était là. On demande à papa ou maman, l'adulte, avant un achat. Hugo range. Maman dit : c'est bien.</t>
+          <t>Hugo garde le ballon rouge tout près. La laine gratte un peu. On chante un petit air. On a demandé à l'adulte. Papa ou maman. La main de l'adulte était là. On demande à papa ou maman, l'adulte, avant un achat. Hugo range. C'est bien.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13313,6 +13707,12 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo garde le ballon rouge tout près. La laine gratte un peu. On chante un petit air. On a demandé à l'adulte. Papa ou maman. La main de l'adulte était là. On demande à papa ou maman, l'adulte, avant un achat. Hugo range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13475,6 +13875,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13499,7 +13904,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Hugo garde le seau bleu tout près. Un pain croustille. On compte jusqu'à trois. On a demandé à l'adulte. Papa ou maman. On a dit : je demande. On demande à papa ou maman, l'adulte, avant un achat. On souffle. Hugo sourit.</t>
+          <t>Hugo garde le seau bleu tout près. Un pain croustille. On compte jusqu'à trois. On a demandé à l'adulte. Papa ou maman. On Je demande. On demande à papa ou maman, l'adulte, avant un achat. On souffle. Hugo sourit.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -13637,6 +14042,13 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo garde le seau bleu tout près. Un pain croustille. On compte jusqu'à trois. On a demandé à l'adulte. Papa ou maman. On
+enfant-f|Je demande. On demande à papa ou maman, l'adulte, avant un achat. On souffle.
+narrateur|Hugo sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13799,6 +14211,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13961,6 +14378,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo garde le doudou tout près. Le savon glisse. On montre du doigt. On a demandé à l'adulte. Papa ou maman. L'adulte a écouté. On demande à papa ou maman, l'adulte, avant un achat. Hugo prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14123,6 +14545,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14147,7 +14574,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Hugo va vers la chambre. Une cuillère tinte. Hugo range. Maman dit : tu as demandé. L'adulte a entendu. On demande à papa ou maman, l'adulte, avant un achat.</t>
+          <t>Hugo va vers la chambre. Une cuillère tinte. Hugo range. Tu as demandé. L'adulte a entendu. On demande à papa ou maman, l'adulte, avant un achat.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14285,6 +14712,12 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo va vers la chambre. Une cuillère tinte. Hugo range.
+maman|Tu as demandé. L'adulte a entendu. On demande à papa ou maman, l'adulte, avant un achat.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14471,6 +14904,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14633,6 +15071,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo garde le ballon rouge tout près. Une plume vole. On range la chaise. On a demandé à l'adulte. Papa ou maman. L'argent est rangé. On demande à papa ou maman, l'adulte, avant un achat. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14795,6 +15238,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14957,6 +15405,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo garde le seau bleu tout près. Le banc est lisse. On range un objet. On a demandé à l'adulte. Papa ou maman. La main de l'adulte était là. On demande à papa ou maman, l'adulte, avant un achat. Maman serre Hugo tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15119,6 +15572,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15143,7 +15601,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Hugo garde le doudou tout près. Un grelot sonne. On se tient la main. On a demandé à l'adulte. Papa ou maman. On a dit : je demande. On demande à papa ou maman, l'adulte, avant un achat. Papa n'est pas loin. On rentre.</t>
+          <t>Hugo garde le doudou tout près. Un grelot sonne. On se tient la main. On a demandé à l'adulte. Papa ou maman. On Je demande. On demande à papa ou maman, l'adulte, avant un achat. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15281,6 +15739,12 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo garde le doudou tout près. Un grelot sonne. On se tient la main. On a demandé à l'adulte. Papa ou maman. On
+enfant-f|Je demande. On demande à papa ou maman, l'adulte, avant un achat. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15443,6 +15907,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15461,7 +15930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15478,6 +15947,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SOC-005.xlsx
+++ b/stories/arbres/TREE-SOC-005.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Hugo répète : demander. Adulte. L'argent se range. Maman range le porte-monnaie. On demande à papa ou maman, l'adulte, avant un achat.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1516,6 +1522,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1685,6 +1692,7 @@
 enfant-m|Je demande. Maman écoute. On demande à papa ou maman, l'adulte, avant un achat.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1868,6 +1876,7 @@
           <t>narrateur|On veut un crayon. On fait quoi ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2039,6 +2048,7 @@
           <t>narrateur|Hugo a demandé. L'adulte a écouté. Demander. On demande à papa ou maman, l'adulte, avant un achat.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2230,6 +2240,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2397,6 +2408,7 @@
           <t>narrateur|Hugo va vers la cuisine. Des miettes dorment sur la table. Dans la cuisine, Hugo voit un gâteau. Hugo demande à l'adulte. Maman écoute. On demande à papa ou maman, l'adulte, avant un achat.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2588,6 +2600,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2755,6 +2768,7 @@
           <t>narrateur|Hugo garde le ballon rouge tout près. La lumière est claire. On souffle doucement. On a demandé à l'adulte. Papa ou maman. L'argent est rangé. On demande à papa ou maman, l'adulte, avant un achat. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2922,6 +2936,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3089,6 +3104,7 @@
           <t>narrateur|Hugo garde le seau bleu tout près. Des miettes dorment sur la table. On écoute jusqu'au bout. On a demandé à l'adulte. Papa ou maman. La main de l'adulte était là. On demande à papa ou maman, l'adulte, avant un achat. Maman serre Hugo tout doux.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3256,6 +3272,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3424,6 +3441,7 @@
 enfant-f|Je demande. On demande à papa ou maman, l'adulte, avant un achat. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3591,6 +3609,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3758,6 +3777,7 @@
           <t>narrateur|Hugo va vers le jardin. Un nuage passe lentement. Dans le jardin, une fleur. Hugo demande avant de cueillir. Adulte. On demande à papa ou maman, l'adulte, avant un achat.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3949,6 +3969,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4117,6 +4138,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4284,6 +4306,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4451,6 +4474,7 @@
           <t>narrateur|Hugo garde le seau bleu tout près. La couverture est douce. On pose les pieds par terre. On a demandé à l'adulte. Papa ou maman. L'argent est rangé. On demande à papa ou maman, l'adulte, avant un achat. On souffle. Hugo sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4618,6 +4642,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4785,6 +4810,7 @@
           <t>narrateur|Hugo garde le doudou tout près. Une cloche tinte au loin. On parle tout bas. On a demandé à l'adulte. Papa ou maman. La main de l'adulte était là. On demande à papa ou maman, l'adulte, avant un achat. Hugo prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4952,6 +4978,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5120,6 +5147,7 @@
 enfant-f|On verra. On demande à papa ou maman, l'adulte, avant un achat.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5311,6 +5339,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5480,6 +5509,7 @@
 narrateur|Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5647,6 +5677,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5814,6 +5845,7 @@
           <t>narrateur|Hugo garde le seau bleu tout près. Une goutte tombe, ploc. On s'assoit un moment. On a demandé à l'adulte. Papa ou maman. L'adulte a écouté. On demande à papa ou maman, l'adulte, avant un achat. Maman serre Hugo tout doux.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5981,6 +6013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6148,6 +6181,7 @@
           <t>narrateur|Hugo garde le doudou tout près. Le savon sent la fleur. On respire, un, deux. On a demandé à l'adulte. Papa ou maman. L'argent est rangé. On demande à papa ou maman, l'adulte, avant un achat. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6315,6 +6349,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6482,6 +6517,7 @@
           <t>narrateur|Après la sieste, un autocollant brille. Hugo va vers maman. Hugo demande. L'adulte écoute. On décide ensemble. On demande à papa ou maman, l'adulte, avant un achat.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6665,6 +6701,7 @@
           <t>narrateur|À qui on demande ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6837,6 +6874,7 @@
 enfant-f|Je demande. On demande à papa ou maman, l'adulte, avant un achat.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7028,6 +7066,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7195,6 +7234,7 @@
           <t>narrateur|Hugo va vers la cuisine. L'herbe chatouille le mollet. Ça sent le pain. Hugo demande. Adulte. Maman sourit. On demande à papa ou maman, l'adulte, avant un achat.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7386,6 +7426,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7554,6 +7595,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7721,6 +7763,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7890,6 +7933,7 @@
 narrateur|Hugo sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8057,6 +8101,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8224,6 +8269,7 @@
           <t>narrateur|Hugo garde le doudou tout près. Le sable est tiède. On met le doudou près. On a demandé à l'adulte. Papa ou maman. L'adulte a écouté. On demande à papa ou maman, l'adulte, avant un achat. Hugo prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8391,6 +8437,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8558,6 +8605,7 @@
           <t>narrateur|Hugo va vers le jardin. La couverture est douce. Une feuille tombe. Hugo demande encore. Demander à l'adulte. On demande à papa ou maman, l'adulte, avant un achat.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8749,6 +8797,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8916,6 +8965,7 @@
           <t>narrateur|Hugo garde le ballon rouge tout près. Un rire court, tout petit. On lace les chaussures. On a demandé à l'adulte. Papa ou maman. L'argent est rangé. On demande à papa ou maman, l'adulte, avant un achat. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9083,6 +9133,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9250,6 +9301,7 @@
           <t>narrateur|Hugo garde le seau bleu tout près. Le papier froisse, chut. On met le manteau. On a demandé à l'adulte. Papa ou maman. La main de l'adulte était là. On demande à papa ou maman, l'adulte, avant un achat. Maman serre Hugo tout doux.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9417,6 +9469,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9585,6 +9638,7 @@
 enfant-f|Je demande. On demande à papa ou maman, l'adulte, avant un achat. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9752,6 +9806,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9919,6 +9974,7 @@
           <t>narrateur|Hugo va vers la chambre. Ça sent le pain tiède. Le doudou écoute. Hugo a demandé. L'adulte était là. On demande à papa ou maman, l'adulte, avant un achat.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10110,6 +10166,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10278,6 +10335,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10445,6 +10503,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10612,6 +10671,7 @@
           <t>narrateur|Hugo garde le seau bleu tout près. La fenêtre vibre un peu. On referme le livre. On a demandé à l'adulte. Papa ou maman. L'argent est rangé. On demande à papa ou maman, l'adulte, avant un achat. On souffle. Hugo sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10779,6 +10839,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10946,6 +11007,7 @@
           <t>narrateur|Hugo garde le doudou tout près. Le lait est froid dans le verre. On pose le ballon. On a demandé à l'adulte. Papa ou maman. La main de l'adulte était là. On demande à papa ou maman, l'adulte, avant un achat. Hugo prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11113,6 +11175,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11280,6 +11343,7 @@
           <t>narrateur|Le soir, un petit carnet. Hugo prend la main de maman. Hugo demande. Adulte. Maman dit merci d'avoir demandé. On demande à papa ou maman, l'adulte, avant un achat.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11463,6 +11527,7 @@
           <t>narrateur|L'argent, on le prend tout seul ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11634,6 +11699,7 @@
           <t>narrateur|Demander. Adulte. Hugo a pris la main de maman. On demande à papa ou maman, l'adulte, avant un achat.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11825,6 +11891,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11992,6 +12059,7 @@
           <t>narrateur|Hugo va vers la cuisine. Le coussin est moelleux. Hugo pose une tasse. Hugo demande. Adulte. Merci. On demande à papa ou maman, l'adulte, avant un achat.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12183,6 +12251,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12352,6 +12421,7 @@
 narrateur|Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12519,6 +12589,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12686,6 +12757,7 @@
           <t>narrateur|Hugo garde le seau bleu tout près. Le savon mousse entre les doigts. On caresse le tissu. On a demandé à l'adulte. Papa ou maman. L'adulte a écouté. On demande à papa ou maman, l'adulte, avant un achat. Maman serre Hugo tout doux.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12853,6 +12925,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13020,6 +13093,7 @@
           <t>narrateur|Hugo garde le doudou tout près. Un ruisseau chante. On tend la main. On a demandé à l'adulte. Papa ou maman. L'argent est rangé. On demande à papa ou maman, l'adulte, avant un achat. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13187,6 +13261,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13354,6 +13429,7 @@
           <t>narrateur|Hugo va vers le jardin. Un vélo passe, toc toc. Le vent est doux. Hugo répète : demander. À l'adulte. On demande à papa ou maman, l'adulte, avant un achat.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13545,6 +13621,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13713,6 +13790,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13880,6 +13958,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14049,6 +14128,7 @@
 narrateur|Hugo sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14216,6 +14296,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14383,6 +14464,7 @@
           <t>narrateur|Hugo garde le doudou tout près. Le savon glisse. On montre du doigt. On a demandé à l'adulte. Papa ou maman. L'adulte a écouté. On demande à papa ou maman, l'adulte, avant un achat. Hugo prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14550,6 +14632,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14718,6 +14801,7 @@
 maman|Tu as demandé. L'adulte a entendu. On demande à papa ou maman, l'adulte, avant un achat.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14909,6 +14993,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15076,6 +15161,7 @@
           <t>narrateur|Hugo garde le ballon rouge tout près. Une plume vole. On range la chaise. On a demandé à l'adulte. Papa ou maman. L'argent est rangé. On demande à papa ou maman, l'adulte, avant un achat. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15243,6 +15329,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15410,6 +15497,7 @@
           <t>narrateur|Hugo garde le seau bleu tout près. Le banc est lisse. On range un objet. On a demandé à l'adulte. Papa ou maman. La main de l'adulte était là. On demande à papa ou maman, l'adulte, avant un achat. Maman serre Hugo tout doux.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15577,6 +15665,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15745,6 +15834,7 @@
 enfant-f|Je demande. On demande à papa ou maman, l'adulte, avant un achat. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15912,6 +16002,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15930,7 +16021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15954,6 +16045,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15968,7 +16073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16155,6 +16260,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
